--- a/data/trans_orig/IP31KM02_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM02_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74030</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>84496</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>60,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>73121</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>63864</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>81318</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>64,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>55,9%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>77235</t>
+          <t>75941</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57655</t>
+          <t>66795</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91017</t>
+          <t>84616</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>150357</t>
+          <t>149971</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126072</t>
+          <t>131394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164684</t>
+          <t>163062</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>48866</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38400</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>66438</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,25%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>54,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>41130</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32933</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>50387</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>36,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,83%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>44,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>59580</t>
+          <t>42657</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45798</t>
+          <t>33982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79160</t>
+          <t>51803</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>100709</t>
+          <t>91523</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86382</t>
+          <t>78432</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124994</t>
+          <t>110100</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>45,59%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>158665</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>143641</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>171741</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>68,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>74,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>115219</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>101258</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>127243</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>61,91%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>54,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>68,37%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>164658</t>
+          <t>117886</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>148259</t>
+          <t>106444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>178454</t>
+          <t>129298</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>71,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>279878</t>
+          <t>276550</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>258851</t>
+          <t>256852</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>298647</t>
+          <t>292913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>71,12%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72576</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59500</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>87600</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>25,73%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>37,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>70895</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>58871</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>84856</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>38,09%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>31,63%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>45,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>82862</t>
+          <t>62707</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69066</t>
+          <t>51295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99261</t>
+          <t>74149</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>153756</t>
+          <t>135283</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134987</t>
+          <t>118920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>174783</t>
+          <t>154981</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>86383</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>73030</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99386</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>51,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>59,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>85344</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>51774</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>105256</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,34%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>95026</t>
+          <t>81616</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81307</t>
+          <t>69725</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108401</t>
+          <t>92556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>180370</t>
+          <t>167999</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>136878</t>
+          <t>151253</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203993</t>
+          <t>185841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>80139</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67136</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>93492</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>48,13%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>56,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>102905</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82993</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>136475</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>54,66%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>72,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>88063</t>
+          <t>73422</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74688</t>
+          <t>62482</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101782</t>
+          <t>85313</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>190969</t>
+          <t>153561</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167346</t>
+          <t>135719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>234461</t>
+          <t>170307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>52,96%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,67 +1754,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>92635</t>
+          <t>91756</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82105</t>
+          <t>80984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103464</t>
+          <t>103505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>48,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>62,29%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>92377</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>81839</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>103257</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>56,33%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>49,91%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>62,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>96701</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>85501</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>108979</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,54%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>62,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>189336</t>
+          <t>184133</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>172962</t>
+          <t>167461</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204761</t>
+          <t>198931</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>60,26%</t>
         </is>
       </c>
     </row>
@@ -1862,74 +1862,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74409</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>62660</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>85181</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,26%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>71884</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>61055</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>82414</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>43,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>37,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>71602</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>60722</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>82140</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>43,67%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>37,03%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>50,09%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>80608</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>68330</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>91808</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,46%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>38,54%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>51,78%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>207</t>
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>152492</t>
+          <t>146011</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>137067</t>
+          <t>131213</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>168866</t>
+          <t>162683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>410834</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>384652</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>434676</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>59,82%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>63,29%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>544</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>366321</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>318794</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>395379</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>60,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>568</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>433620</t>
+          <t>367819</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>403613</t>
+          <t>346615</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>461505</t>
+          <t>386977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>799941</t>
+          <t>778653</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>747858</t>
+          <t>744514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>839350</t>
+          <t>813442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>275990</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>252148</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>302172</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>44,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>286813</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>257755</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>334340</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>51,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>311113</t>
+          <t>250389</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283228</t>
+          <t>231231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>341120</t>
+          <t>271593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>597926</t>
+          <t>526378</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>558517</t>
+          <t>491589</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>650009</t>
+          <t>560517</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>42,95%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
